--- a/src/test/resources/testdata/Opencart_LoginData.xlsx
+++ b/src/test/resources/testdata/Opencart_LoginData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspaces\15-Sept-2023batch\opencart\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\SeleniumFramework\SeleniumJavaFramework\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3315BD60-ACC2-4D41-9A18-B0F87EEF7991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D0871F-32A2-47BB-BFCC-12EAB9BB7EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="17589" xr2:uid="{1F2D179E-37D2-4BC0-88A9-F5C135B87DA5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1F2D179E-37D2-4BC0-88A9-F5C135B87DA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -69,13 +69,13 @@
     <t>xyz</t>
   </si>
   <si>
-    <t>pavanoltraining@gmail.com</t>
-  </si>
-  <si>
-    <t>test@123</t>
-  </si>
-  <si>
-    <t>abc123@gmail.com</t>
+    <t>testing01a@gmail.com</t>
+  </si>
+  <si>
+    <t>Password1!</t>
+  </si>
+  <si>
+    <t>testing01b@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -170,7 +170,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -192,9 +192,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -232,7 +232,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -338,7 +338,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -480,7 +480,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -489,14 +489,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884FCF78-0A3E-40BF-9E26-11C478AF56E2}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.23046875" customWidth="1"/>
-    <col min="2" max="2" width="17.3046875" customWidth="1"/>
-    <col min="3" max="3" width="18.15234375" customWidth="1"/>
+    <col min="1" max="1" width="37.26953125" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" customWidth="1"/>
+    <col min="3" max="3" width="18.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -507,8 +507,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:3" ht="21" x14ac:dyDescent="0.5">
+      <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -518,7 +518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:3" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -529,7 +529,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.5">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -540,7 +540,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.5">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -551,14 +551,14 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="20.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.5">
+      <c r="A6" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -568,9 +568,9 @@
     <hyperlink ref="A4" r:id="rId2" xr:uid="{8456409A-CACC-4B7E-B78E-75E713148E0E}"/>
     <hyperlink ref="A3" r:id="rId3" xr:uid="{5E52A498-5B14-4BDC-BBF1-05425B8AC197}"/>
     <hyperlink ref="A5" r:id="rId4" xr:uid="{94E9D5A6-98A1-4A25-BDDE-C5B20EDA887E}"/>
-    <hyperlink ref="B2" r:id="rId5" xr:uid="{968262D0-AE14-41EF-AB8A-08B3F886E797}"/>
+    <hyperlink ref="B2" r:id="rId5" display="test@123" xr:uid="{968262D0-AE14-41EF-AB8A-08B3F886E797}"/>
     <hyperlink ref="A6" r:id="rId6" xr:uid="{75A4F8D6-7BF1-446B-9367-475FA4FB44C7}"/>
-    <hyperlink ref="B6" r:id="rId7" xr:uid="{01D5649A-5E55-45E1-9B81-1CE430C208A1}"/>
+    <hyperlink ref="B6" r:id="rId7" display="test@123" xr:uid="{01D5649A-5E55-45E1-9B81-1CE430C208A1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId8"/>

--- a/src/test/resources/testdata/Opencart_LoginData.xlsx
+++ b/src/test/resources/testdata/Opencart_LoginData.xlsx
@@ -3,21 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\SeleniumFramework\SeleniumJavaFramework\src\test\resources\testdata\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D0871F-32A2-47BB-BFCC-12EAB9BB7EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{15956640-84E5-41D5-A53B-E8F1A80C7E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1F2D179E-37D2-4BC0-88A9-F5C135B87DA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
   <si>
     <t>username</t>
   </si>
@@ -76,12 +72,22 @@
   </si>
   <si>
     <t>testing01b@gmail.com</t>
+  </si>
+  <si>
+    <t>test@gmail.com</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>FAIL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -114,7 +120,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -125,6 +131,26 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
       </patternFill>
     </fill>
   </fills>
@@ -156,7 +182,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -173,6 +199,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -488,12 +526,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884FCF78-0A3E-40BF-9E26-11C478AF56E2}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.26953125" customWidth="1"/>
-    <col min="2" max="2" width="17.26953125" customWidth="1"/>
-    <col min="3" max="3" width="18.1796875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="37.26953125"/>
+    <col min="2" max="2" customWidth="true" width="17.26953125"/>
+    <col min="3" max="3" customWidth="true" width="18.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.5">
@@ -517,9 +555,12 @@
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="D2" t="s" s="9">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" spans="1:3" ht="21" x14ac:dyDescent="0.5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -528,9 +569,12 @@
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="D3" t="s" s="10">
+        <v>16</v>
+      </c>
     </row>
     <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.5">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -538,6 +582,9 @@
       </c>
       <c r="C4" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="D4" t="s" s="11">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.5">
@@ -550,6 +597,9 @@
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="D5" t="s" s="12">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.5">
       <c r="A6" s="5" t="s">
@@ -560,6 +610,33 @@
       </c>
       <c r="C6" s="3" t="s">
         <v>5</v>
+      </c>
+      <c r="D6" t="s" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.5">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="21" x14ac:dyDescent="0.5">
+      <c r="A8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s" s="15">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -571,8 +648,9 @@
     <hyperlink ref="B2" r:id="rId5" display="test@123" xr:uid="{968262D0-AE14-41EF-AB8A-08B3F886E797}"/>
     <hyperlink ref="A6" r:id="rId6" xr:uid="{75A4F8D6-7BF1-446B-9367-475FA4FB44C7}"/>
     <hyperlink ref="B6" r:id="rId7" display="test@123" xr:uid="{01D5649A-5E55-45E1-9B81-1CE430C208A1}"/>
+    <hyperlink ref="A8" r:id="rId8" xr:uid="{D8CF08B4-ED93-48C4-8916-969CACA41A0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId8"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId9"/>
 </worksheet>
 </file>
--- a/src/test/resources/testdata/Opencart_LoginData.xlsx
+++ b/src/test/resources/testdata/Opencart_LoginData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{15956640-84E5-41D5-A53B-E8F1A80C7E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{32DCD2B4-A5DE-4194-AB44-F2D103F3B3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1F2D179E-37D2-4BC0-88A9-F5C135B87DA5}"/>
   </bookViews>
@@ -16,21 +16,12 @@
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t>username</t>
   </si>
@@ -41,9 +32,6 @@
     <t>res</t>
   </si>
   <si>
-    <t>lakshmi@yahoo.com</t>
-  </si>
-  <si>
     <t>Lakshmi</t>
   </si>
   <si>
@@ -53,9 +41,6 @@
     <t>laksh@yahoo.com</t>
   </si>
   <si>
-    <t>Laxmi</t>
-  </si>
-  <si>
     <t>Invalid</t>
   </si>
   <si>
@@ -80,7 +65,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>FAIL</t>
+    <t>ERROR</t>
   </si>
 </sst>
 </file>
@@ -120,7 +105,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -134,23 +119,18 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="none">
+      <patternFill patternType="solid">
         <fgColor indexed="17"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="17"/>
+        <fgColor indexed="10"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="none">
-        <fgColor indexed="10"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="10"/>
+        <fgColor indexed="17"/>
       </patternFill>
     </fill>
   </fills>
@@ -200,17 +180,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -534,7 +512,7 @@
     <col min="3" max="3" customWidth="true" width="18.1796875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -545,112 +523,98 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="21" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:4" ht="21" x14ac:dyDescent="0.5">
       <c r="A2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s" s="10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" customFormat="1" ht="21" x14ac:dyDescent="0.5">
+      <c r="A3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" customFormat="1" ht="21" x14ac:dyDescent="0.5">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s" s="12">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" customFormat="1" ht="21" x14ac:dyDescent="0.5">
+      <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" customFormat="1" ht="21" x14ac:dyDescent="0.5">
+      <c r="A6" s="6"/>
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s" s="14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" customFormat="1" ht="21" x14ac:dyDescent="0.5">
+      <c r="A7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s" s="9">
-        <v>15</v>
+      <c r="B7" s="6"/>
+      <c r="C7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s" s="15">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="21" x14ac:dyDescent="0.5">
-      <c r="A3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s" s="10">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.5">
-      <c r="A4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s" s="11">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.5">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s" s="12">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.5">
-      <c r="A6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s" s="13">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.5">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s" s="14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="21" x14ac:dyDescent="0.5">
-      <c r="A8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" t="s" s="15">
-        <v>15</v>
-      </c>
-    </row>
+    <row r="8" spans="1:4" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{D3BE7519-95C3-4ACD-9AB4-5385C9508082}"/>
-    <hyperlink ref="A4" r:id="rId2" xr:uid="{8456409A-CACC-4B7E-B78E-75E713148E0E}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{5E52A498-5B14-4BDC-BBF1-05425B8AC197}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{94E9D5A6-98A1-4A25-BDDE-C5B20EDA887E}"/>
-    <hyperlink ref="B2" r:id="rId5" display="test@123" xr:uid="{968262D0-AE14-41EF-AB8A-08B3F886E797}"/>
-    <hyperlink ref="A6" r:id="rId6" xr:uid="{75A4F8D6-7BF1-446B-9367-475FA4FB44C7}"/>
-    <hyperlink ref="B6" r:id="rId7" display="test@123" xr:uid="{01D5649A-5E55-45E1-9B81-1CE430C208A1}"/>
-    <hyperlink ref="A8" r:id="rId8" xr:uid="{D8CF08B4-ED93-48C4-8916-969CACA41A0E}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{8456409A-CACC-4B7E-B78E-75E713148E0E}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{94E9D5A6-98A1-4A25-BDDE-C5B20EDA887E}"/>
+    <hyperlink ref="B2" r:id="rId4" display="test@123" xr:uid="{968262D0-AE14-41EF-AB8A-08B3F886E797}"/>
+    <hyperlink ref="A5" r:id="rId5" xr:uid="{75A4F8D6-7BF1-446B-9367-475FA4FB44C7}"/>
+    <hyperlink ref="B5" r:id="rId6" display="test@123" xr:uid="{01D5649A-5E55-45E1-9B81-1CE430C208A1}"/>
+    <hyperlink ref="A7" r:id="rId7" xr:uid="{D8CF08B4-ED93-48C4-8916-969CACA41A0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId9"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId8"/>
 </worksheet>
 </file>
--- a/src/test/resources/testdata/Opencart_LoginData.xlsx
+++ b/src/test/resources/testdata/Opencart_LoginData.xlsx
@@ -3,7 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{32DCD2B4-A5DE-4194-AB44-F2D103F3B3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\SeleniumFramework\SeleniumJavaFramework\src\test\resources\testdata\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE3D1F2-DE73-4738-A5A7-5041F35950FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1F2D179E-37D2-4BC0-88A9-F5C135B87DA5}"/>
   </bookViews>
@@ -11,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -47,9 +51,6 @@
     <t>laks@yahoo.com</t>
   </si>
   <si>
-    <t>xyz</t>
-  </si>
-  <si>
     <t>testing01a@gmail.com</t>
   </si>
   <si>
@@ -65,7 +66,10 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>ERROR</t>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>xyz123fed3</t>
   </si>
 </sst>
 </file>
@@ -504,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884FCF78-0A3E-40BF-9E26-11C478AF56E2}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="37.26953125"/>
@@ -525,19 +529,19 @@
     </row>
     <row r="2" spans="1:4" ht="21" x14ac:dyDescent="0.5">
       <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" customFormat="1" ht="21" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:4" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -548,62 +552,61 @@
         <v>4</v>
       </c>
       <c r="D3" t="s" s="11">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4" customFormat="1" ht="21" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:4" ht="21" x14ac:dyDescent="0.5">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D4" t="s" s="12">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" customFormat="1" ht="21" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:4" ht="21" x14ac:dyDescent="0.5">
       <c r="A5" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D5" t="s" s="13">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" customFormat="1" ht="21" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:4" ht="21" x14ac:dyDescent="0.5">
       <c r="A6" s="6"/>
       <c r="B6" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D6" t="s" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" customFormat="1" ht="21" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:4" ht="21" x14ac:dyDescent="0.5">
       <c r="A7" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D7" t="s" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:4" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{D3BE7519-95C3-4ACD-9AB4-5385C9508082}"/>

--- a/src/test/resources/testdata/Opencart_LoginData.xlsx
+++ b/src/test/resources/testdata/Opencart_LoginData.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="16">
   <si>
     <t>username</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>xyz123fed3</t>
+  </si>
+  <si>
+    <t>ERROR</t>
   </si>
 </sst>
 </file>
@@ -109,7 +112,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -135,6 +138,11 @@
     <fill>
       <patternFill patternType="none">
         <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="10"/>
       </patternFill>
     </fill>
   </fills>
@@ -166,7 +174,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -193,6 +201,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -537,7 +548,7 @@
       <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s" s="10">
+      <c r="D2" t="s" s="16">
         <v>12</v>
       </c>
     </row>
@@ -551,7 +562,7 @@
       <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" t="s" s="11">
+      <c r="D3" t="s" s="17">
         <v>12</v>
       </c>
     </row>
@@ -565,8 +576,8 @@
       <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s" s="12">
-        <v>12</v>
+      <c r="D4" t="s" s="18">
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="21" x14ac:dyDescent="0.5">
